--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F388"/>
+  <dimension ref="A1:F532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11284,6 +11284,4038 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>502</v>
+      </c>
+      <c r="E389" t="n">
+        <v>5</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>502</v>
+      </c>
+      <c r="E390" t="n">
+        <v>5</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>502</v>
+      </c>
+      <c r="E391" t="n">
+        <v>5</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>502</v>
+      </c>
+      <c r="E392" t="n">
+        <v>5</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>502</v>
+      </c>
+      <c r="E393" t="n">
+        <v>5</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>502</v>
+      </c>
+      <c r="E394" t="n">
+        <v>5</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>502</v>
+      </c>
+      <c r="E395" t="n">
+        <v>5</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>502</v>
+      </c>
+      <c r="E396" t="n">
+        <v>5</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>502</v>
+      </c>
+      <c r="E397" t="n">
+        <v>5</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>502</v>
+      </c>
+      <c r="E398" t="n">
+        <v>5</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>502</v>
+      </c>
+      <c r="E399" t="n">
+        <v>5</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>502</v>
+      </c>
+      <c r="E400" t="n">
+        <v>5</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>502</v>
+      </c>
+      <c r="E401" t="n">
+        <v>5</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>502</v>
+      </c>
+      <c r="E402" t="n">
+        <v>5</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-07-30 06:59:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>502</v>
+      </c>
+      <c r="E403" t="n">
+        <v>5</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>502</v>
+      </c>
+      <c r="E404" t="n">
+        <v>5</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>502</v>
+      </c>
+      <c r="E405" t="n">
+        <v>5</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>502</v>
+      </c>
+      <c r="E406" t="n">
+        <v>5</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>502</v>
+      </c>
+      <c r="E407" t="n">
+        <v>5</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>502</v>
+      </c>
+      <c r="E408" t="n">
+        <v>5</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>502</v>
+      </c>
+      <c r="E409" t="n">
+        <v>5</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>502</v>
+      </c>
+      <c r="E410" t="n">
+        <v>5</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:00:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>502</v>
+      </c>
+      <c r="E411" t="n">
+        <v>5</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>502</v>
+      </c>
+      <c r="E412" t="n">
+        <v>5</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>502</v>
+      </c>
+      <c r="E413" t="n">
+        <v>5</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>502</v>
+      </c>
+      <c r="E414" t="n">
+        <v>5</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>502</v>
+      </c>
+      <c r="E415" t="n">
+        <v>5</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>502</v>
+      </c>
+      <c r="E416" t="n">
+        <v>5</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>502</v>
+      </c>
+      <c r="E417" t="n">
+        <v>5</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:01:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>502</v>
+      </c>
+      <c r="E418" t="n">
+        <v>5</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>502</v>
+      </c>
+      <c r="E419" t="n">
+        <v>5</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>502</v>
+      </c>
+      <c r="E420" t="n">
+        <v>5</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>502</v>
+      </c>
+      <c r="E421" t="n">
+        <v>5</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>502</v>
+      </c>
+      <c r="E422" t="n">
+        <v>5</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>502</v>
+      </c>
+      <c r="E423" t="n">
+        <v>5</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>502</v>
+      </c>
+      <c r="E424" t="n">
+        <v>5</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:02:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>502</v>
+      </c>
+      <c r="E425" t="n">
+        <v>5</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>502</v>
+      </c>
+      <c r="E426" t="n">
+        <v>5</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>502</v>
+      </c>
+      <c r="E427" t="n">
+        <v>5</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>502</v>
+      </c>
+      <c r="E428" t="n">
+        <v>5</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>502</v>
+      </c>
+      <c r="E429" t="n">
+        <v>5</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>502</v>
+      </c>
+      <c r="E430" t="n">
+        <v>5</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>502</v>
+      </c>
+      <c r="E431" t="n">
+        <v>5</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>502</v>
+      </c>
+      <c r="E432" t="n">
+        <v>5</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:03:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>502</v>
+      </c>
+      <c r="E433" t="n">
+        <v>5</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>502</v>
+      </c>
+      <c r="E434" t="n">
+        <v>5</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>502</v>
+      </c>
+      <c r="E435" t="n">
+        <v>5</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>502</v>
+      </c>
+      <c r="E436" t="n">
+        <v>5</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>502</v>
+      </c>
+      <c r="E437" t="n">
+        <v>5</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>502</v>
+      </c>
+      <c r="E438" t="n">
+        <v>5</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>502</v>
+      </c>
+      <c r="E439" t="n">
+        <v>5</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:04:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>502</v>
+      </c>
+      <c r="E440" t="n">
+        <v>5</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>502</v>
+      </c>
+      <c r="E441" t="n">
+        <v>5</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>502</v>
+      </c>
+      <c r="E442" t="n">
+        <v>5</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>502</v>
+      </c>
+      <c r="E443" t="n">
+        <v>5</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>502</v>
+      </c>
+      <c r="E444" t="n">
+        <v>5</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>502</v>
+      </c>
+      <c r="E445" t="n">
+        <v>5</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>502</v>
+      </c>
+      <c r="E446" t="n">
+        <v>5</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>502</v>
+      </c>
+      <c r="E447" t="n">
+        <v>5</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>502</v>
+      </c>
+      <c r="E448" t="n">
+        <v>5</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>502</v>
+      </c>
+      <c r="E449" t="n">
+        <v>5</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>502</v>
+      </c>
+      <c r="E450" t="n">
+        <v>5</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>502</v>
+      </c>
+      <c r="E451" t="n">
+        <v>5</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>502</v>
+      </c>
+      <c r="E452" t="n">
+        <v>5</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>502</v>
+      </c>
+      <c r="E453" t="n">
+        <v>5</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:06:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>502</v>
+      </c>
+      <c r="E454" t="n">
+        <v>5</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>502</v>
+      </c>
+      <c r="E455" t="n">
+        <v>5</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>502</v>
+      </c>
+      <c r="E456" t="n">
+        <v>5</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>502</v>
+      </c>
+      <c r="E457" t="n">
+        <v>5</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>502</v>
+      </c>
+      <c r="E458" t="n">
+        <v>5</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>502</v>
+      </c>
+      <c r="E459" t="n">
+        <v>5</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>502</v>
+      </c>
+      <c r="E460" t="n">
+        <v>5</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>502</v>
+      </c>
+      <c r="E461" t="n">
+        <v>5</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:07:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>502</v>
+      </c>
+      <c r="E462" t="n">
+        <v>5</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>502</v>
+      </c>
+      <c r="E463" t="n">
+        <v>5</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>502</v>
+      </c>
+      <c r="E464" t="n">
+        <v>5</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>502</v>
+      </c>
+      <c r="E465" t="n">
+        <v>5</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>502</v>
+      </c>
+      <c r="E466" t="n">
+        <v>5</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>502</v>
+      </c>
+      <c r="E467" t="n">
+        <v>5</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>502</v>
+      </c>
+      <c r="E468" t="n">
+        <v>5</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>502</v>
+      </c>
+      <c r="E469" t="n">
+        <v>5</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>502</v>
+      </c>
+      <c r="E470" t="n">
+        <v>5</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>502</v>
+      </c>
+      <c r="E471" t="n">
+        <v>5</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>502</v>
+      </c>
+      <c r="E472" t="n">
+        <v>5</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>502</v>
+      </c>
+      <c r="E473" t="n">
+        <v>5</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>502</v>
+      </c>
+      <c r="E474" t="n">
+        <v>5</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>502</v>
+      </c>
+      <c r="E475" t="n">
+        <v>5</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>502</v>
+      </c>
+      <c r="E476" t="n">
+        <v>5</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>502</v>
+      </c>
+      <c r="E477" t="n">
+        <v>5</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>502</v>
+      </c>
+      <c r="E478" t="n">
+        <v>5</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>502</v>
+      </c>
+      <c r="E479" t="n">
+        <v>5</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>502</v>
+      </c>
+      <c r="E480" t="n">
+        <v>5</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>502</v>
+      </c>
+      <c r="E481" t="n">
+        <v>5</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>502</v>
+      </c>
+      <c r="E482" t="n">
+        <v>5</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>502</v>
+      </c>
+      <c r="E483" t="n">
+        <v>5</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>502</v>
+      </c>
+      <c r="E484" t="n">
+        <v>5</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>502</v>
+      </c>
+      <c r="E485" t="n">
+        <v>5</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>502</v>
+      </c>
+      <c r="E486" t="n">
+        <v>5</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>502</v>
+      </c>
+      <c r="E487" t="n">
+        <v>5</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>502</v>
+      </c>
+      <c r="E488" t="n">
+        <v>5</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>502</v>
+      </c>
+      <c r="E489" t="n">
+        <v>5</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>502</v>
+      </c>
+      <c r="E490" t="n">
+        <v>5</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:11:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>502</v>
+      </c>
+      <c r="E491" t="n">
+        <v>5</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>502</v>
+      </c>
+      <c r="E492" t="n">
+        <v>5</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>502</v>
+      </c>
+      <c r="E493" t="n">
+        <v>5</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>502</v>
+      </c>
+      <c r="E494" t="n">
+        <v>5</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>502</v>
+      </c>
+      <c r="E495" t="n">
+        <v>5</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>502</v>
+      </c>
+      <c r="E496" t="n">
+        <v>5</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>502</v>
+      </c>
+      <c r="E497" t="n">
+        <v>5</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:12:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>502</v>
+      </c>
+      <c r="E498" t="n">
+        <v>5</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>502</v>
+      </c>
+      <c r="E499" t="n">
+        <v>5</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>502</v>
+      </c>
+      <c r="E500" t="n">
+        <v>5</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>502</v>
+      </c>
+      <c r="E501" t="n">
+        <v>5</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>502</v>
+      </c>
+      <c r="E502" t="n">
+        <v>5</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>502</v>
+      </c>
+      <c r="E503" t="n">
+        <v>5</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>502</v>
+      </c>
+      <c r="E504" t="n">
+        <v>5</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>502</v>
+      </c>
+      <c r="E505" t="n">
+        <v>5</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:13:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>502</v>
+      </c>
+      <c r="E506" t="n">
+        <v>5</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>502</v>
+      </c>
+      <c r="E507" t="n">
+        <v>5</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>502</v>
+      </c>
+      <c r="E508" t="n">
+        <v>5</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>502</v>
+      </c>
+      <c r="E509" t="n">
+        <v>5</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>502</v>
+      </c>
+      <c r="E510" t="n">
+        <v>5</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>502</v>
+      </c>
+      <c r="E511" t="n">
+        <v>5</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>502</v>
+      </c>
+      <c r="E512" t="n">
+        <v>5</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:14:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>502</v>
+      </c>
+      <c r="E513" t="n">
+        <v>5</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>502</v>
+      </c>
+      <c r="E514" t="n">
+        <v>5</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>502</v>
+      </c>
+      <c r="E515" t="n">
+        <v>5</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>502</v>
+      </c>
+      <c r="E516" t="n">
+        <v>5</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>502</v>
+      </c>
+      <c r="E517" t="n">
+        <v>5</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>502</v>
+      </c>
+      <c r="E518" t="n">
+        <v>5</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>502</v>
+      </c>
+      <c r="E519" t="n">
+        <v>5</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:15:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>502</v>
+      </c>
+      <c r="E520" t="n">
+        <v>5</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>502</v>
+      </c>
+      <c r="E521" t="n">
+        <v>5</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>502</v>
+      </c>
+      <c r="E522" t="n">
+        <v>5</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>502</v>
+      </c>
+      <c r="E523" t="n">
+        <v>5</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>502</v>
+      </c>
+      <c r="E524" t="n">
+        <v>5</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>502</v>
+      </c>
+      <c r="E525" t="n">
+        <v>5</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>502</v>
+      </c>
+      <c r="E526" t="n">
+        <v>5</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:16:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>502</v>
+      </c>
+      <c r="E527" t="n">
+        <v>5</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:17:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>5</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:17:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>0</v>
+      </c>
+      <c r="E529" t="n">
+        <v>5</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:19:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>5</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:20:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>0</v>
+      </c>
+      <c r="E531" t="n">
+        <v>5</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:22:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>5</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-07-30 07:23:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F532"/>
+  <dimension ref="A1:F388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11284,4038 +11284,6 @@
         </is>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D389" t="n">
-        <v>502</v>
-      </c>
-      <c r="E389" t="n">
-        <v>5</v>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D390" t="n">
-        <v>502</v>
-      </c>
-      <c r="E390" t="n">
-        <v>5</v>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D391" t="n">
-        <v>502</v>
-      </c>
-      <c r="E391" t="n">
-        <v>5</v>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C392" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D392" t="n">
-        <v>502</v>
-      </c>
-      <c r="E392" t="n">
-        <v>5</v>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C393" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D393" t="n">
-        <v>502</v>
-      </c>
-      <c r="E393" t="n">
-        <v>5</v>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D394" t="n">
-        <v>502</v>
-      </c>
-      <c r="E394" t="n">
-        <v>5</v>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D395" t="n">
-        <v>502</v>
-      </c>
-      <c r="E395" t="n">
-        <v>5</v>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=038FB0CBBC4030320C033CC1E31C486C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D396" t="n">
-        <v>502</v>
-      </c>
-      <c r="E396" t="n">
-        <v>5</v>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D397" t="n">
-        <v>502</v>
-      </c>
-      <c r="E397" t="n">
-        <v>5</v>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D398" t="n">
-        <v>502</v>
-      </c>
-      <c r="E398" t="n">
-        <v>5</v>
-      </c>
-      <c r="F398" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D399" t="n">
-        <v>502</v>
-      </c>
-      <c r="E399" t="n">
-        <v>5</v>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D400" t="n">
-        <v>502</v>
-      </c>
-      <c r="E400" t="n">
-        <v>5</v>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D401" t="n">
-        <v>502</v>
-      </c>
-      <c r="E401" t="n">
-        <v>5</v>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D402" t="n">
-        <v>502</v>
-      </c>
-      <c r="E402" t="n">
-        <v>5</v>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>2026-07-30 06:59:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D403" t="n">
-        <v>502</v>
-      </c>
-      <c r="E403" t="n">
-        <v>5</v>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D404" t="n">
-        <v>502</v>
-      </c>
-      <c r="E404" t="n">
-        <v>5</v>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D405" t="n">
-        <v>502</v>
-      </c>
-      <c r="E405" t="n">
-        <v>5</v>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D406" t="n">
-        <v>502</v>
-      </c>
-      <c r="E406" t="n">
-        <v>5</v>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D407" t="n">
-        <v>502</v>
-      </c>
-      <c r="E407" t="n">
-        <v>5</v>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>502</v>
-      </c>
-      <c r="E408" t="n">
-        <v>5</v>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C409" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D409" t="n">
-        <v>502</v>
-      </c>
-      <c r="E409" t="n">
-        <v>5</v>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D410" t="n">
-        <v>502</v>
-      </c>
-      <c r="E410" t="n">
-        <v>5</v>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:00:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C411" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D411" t="n">
-        <v>502</v>
-      </c>
-      <c r="E411" t="n">
-        <v>5</v>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=516EBE32C975E9F3B642F3476A79355D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C412" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D412" t="n">
-        <v>502</v>
-      </c>
-      <c r="E412" t="n">
-        <v>5</v>
-      </c>
-      <c r="F412" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D413" t="n">
-        <v>502</v>
-      </c>
-      <c r="E413" t="n">
-        <v>5</v>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D414" t="n">
-        <v>502</v>
-      </c>
-      <c r="E414" t="n">
-        <v>5</v>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D415" t="n">
-        <v>502</v>
-      </c>
-      <c r="E415" t="n">
-        <v>5</v>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D416" t="n">
-        <v>502</v>
-      </c>
-      <c r="E416" t="n">
-        <v>5</v>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D417" t="n">
-        <v>502</v>
-      </c>
-      <c r="E417" t="n">
-        <v>5</v>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:01:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D418" t="n">
-        <v>502</v>
-      </c>
-      <c r="E418" t="n">
-        <v>5</v>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D419" t="n">
-        <v>502</v>
-      </c>
-      <c r="E419" t="n">
-        <v>5</v>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D420" t="n">
-        <v>502</v>
-      </c>
-      <c r="E420" t="n">
-        <v>5</v>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D421" t="n">
-        <v>502</v>
-      </c>
-      <c r="E421" t="n">
-        <v>5</v>
-      </c>
-      <c r="F421" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D422" t="n">
-        <v>502</v>
-      </c>
-      <c r="E422" t="n">
-        <v>5</v>
-      </c>
-      <c r="F422" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>502</v>
-      </c>
-      <c r="E423" t="n">
-        <v>5</v>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>502</v>
-      </c>
-      <c r="E424" t="n">
-        <v>5</v>
-      </c>
-      <c r="F424" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:02:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>502</v>
-      </c>
-      <c r="E425" t="n">
-        <v>5</v>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>502</v>
-      </c>
-      <c r="E426" t="n">
-        <v>5</v>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F6D0C53BE584D9DB3E33593D1E5674E0?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>502</v>
-      </c>
-      <c r="E427" t="n">
-        <v>5</v>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>502</v>
-      </c>
-      <c r="E428" t="n">
-        <v>5</v>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>502</v>
-      </c>
-      <c r="E429" t="n">
-        <v>5</v>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>502</v>
-      </c>
-      <c r="E430" t="n">
-        <v>5</v>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>502</v>
-      </c>
-      <c r="E431" t="n">
-        <v>5</v>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>502</v>
-      </c>
-      <c r="E432" t="n">
-        <v>5</v>
-      </c>
-      <c r="F432" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:03:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>502</v>
-      </c>
-      <c r="E433" t="n">
-        <v>5</v>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>502</v>
-      </c>
-      <c r="E434" t="n">
-        <v>5</v>
-      </c>
-      <c r="F434" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>502</v>
-      </c>
-      <c r="E435" t="n">
-        <v>5</v>
-      </c>
-      <c r="F435" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>502</v>
-      </c>
-      <c r="E436" t="n">
-        <v>5</v>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>502</v>
-      </c>
-      <c r="E437" t="n">
-        <v>5</v>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D438" t="n">
-        <v>502</v>
-      </c>
-      <c r="E438" t="n">
-        <v>5</v>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D439" t="n">
-        <v>502</v>
-      </c>
-      <c r="E439" t="n">
-        <v>5</v>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:04:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B440" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C440" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D440" t="n">
-        <v>502</v>
-      </c>
-      <c r="E440" t="n">
-        <v>5</v>
-      </c>
-      <c r="F440" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C441" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D441" t="n">
-        <v>502</v>
-      </c>
-      <c r="E441" t="n">
-        <v>5</v>
-      </c>
-      <c r="F441" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D1BDC7CB42BA86E52479239FB94493C5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D442" t="n">
-        <v>502</v>
-      </c>
-      <c r="E442" t="n">
-        <v>5</v>
-      </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D443" t="n">
-        <v>502</v>
-      </c>
-      <c r="E443" t="n">
-        <v>5</v>
-      </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D444" t="n">
-        <v>502</v>
-      </c>
-      <c r="E444" t="n">
-        <v>5</v>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D445" t="n">
-        <v>502</v>
-      </c>
-      <c r="E445" t="n">
-        <v>5</v>
-      </c>
-      <c r="F445" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D446" t="n">
-        <v>502</v>
-      </c>
-      <c r="E446" t="n">
-        <v>5</v>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:05:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D447" t="n">
-        <v>502</v>
-      </c>
-      <c r="E447" t="n">
-        <v>5</v>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D448" t="n">
-        <v>502</v>
-      </c>
-      <c r="E448" t="n">
-        <v>5</v>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D449" t="n">
-        <v>502</v>
-      </c>
-      <c r="E449" t="n">
-        <v>5</v>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D450" t="n">
-        <v>502</v>
-      </c>
-      <c r="E450" t="n">
-        <v>5</v>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D451" t="n">
-        <v>502</v>
-      </c>
-      <c r="E451" t="n">
-        <v>5</v>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D452" t="n">
-        <v>502</v>
-      </c>
-      <c r="E452" t="n">
-        <v>5</v>
-      </c>
-      <c r="F452" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B453" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C453" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D453" t="n">
-        <v>502</v>
-      </c>
-      <c r="E453" t="n">
-        <v>5</v>
-      </c>
-      <c r="F453" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:06:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B454" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C454" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D454" t="n">
-        <v>502</v>
-      </c>
-      <c r="E454" t="n">
-        <v>5</v>
-      </c>
-      <c r="F454" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D455" t="n">
-        <v>502</v>
-      </c>
-      <c r="E455" t="n">
-        <v>5</v>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D456" t="n">
-        <v>502</v>
-      </c>
-      <c r="E456" t="n">
-        <v>5</v>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DEBB50A7A909FAF319FC2360E5ED52AA?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D457" t="n">
-        <v>502</v>
-      </c>
-      <c r="E457" t="n">
-        <v>5</v>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D458" t="n">
-        <v>502</v>
-      </c>
-      <c r="E458" t="n">
-        <v>5</v>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D459" t="n">
-        <v>502</v>
-      </c>
-      <c r="E459" t="n">
-        <v>5</v>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:41</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D460" t="n">
-        <v>502</v>
-      </c>
-      <c r="E460" t="n">
-        <v>5</v>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D461" t="n">
-        <v>502</v>
-      </c>
-      <c r="E461" t="n">
-        <v>5</v>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:07:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D462" t="n">
-        <v>502</v>
-      </c>
-      <c r="E462" t="n">
-        <v>5</v>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D463" t="n">
-        <v>502</v>
-      </c>
-      <c r="E463" t="n">
-        <v>5</v>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:14</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D464" t="n">
-        <v>502</v>
-      </c>
-      <c r="E464" t="n">
-        <v>5</v>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C465" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D465" t="n">
-        <v>502</v>
-      </c>
-      <c r="E465" t="n">
-        <v>5</v>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B466" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C466" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D466" t="n">
-        <v>502</v>
-      </c>
-      <c r="E466" t="n">
-        <v>5</v>
-      </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B467" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C467" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D467" t="n">
-        <v>502</v>
-      </c>
-      <c r="E467" t="n">
-        <v>5</v>
-      </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D468" t="n">
-        <v>502</v>
-      </c>
-      <c r="E468" t="n">
-        <v>5</v>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:08:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B469" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D469" t="n">
-        <v>502</v>
-      </c>
-      <c r="E469" t="n">
-        <v>5</v>
-      </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B470" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D470" t="n">
-        <v>502</v>
-      </c>
-      <c r="E470" t="n">
-        <v>5</v>
-      </c>
-      <c r="F470" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D471" t="n">
-        <v>502</v>
-      </c>
-      <c r="E471" t="n">
-        <v>5</v>
-      </c>
-      <c r="F471" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B472" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DB85860FF0169556E36AA79C3F65F42C?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C472" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D472" t="n">
-        <v>502</v>
-      </c>
-      <c r="E472" t="n">
-        <v>5</v>
-      </c>
-      <c r="F472" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B473" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D473" t="n">
-        <v>502</v>
-      </c>
-      <c r="E473" t="n">
-        <v>5</v>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B474" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D474" t="n">
-        <v>502</v>
-      </c>
-      <c r="E474" t="n">
-        <v>5</v>
-      </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B475" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D475" t="n">
-        <v>502</v>
-      </c>
-      <c r="E475" t="n">
-        <v>5</v>
-      </c>
-      <c r="F475" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:09:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B476" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C476" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D476" t="n">
-        <v>502</v>
-      </c>
-      <c r="E476" t="n">
-        <v>5</v>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B477" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D477" t="n">
-        <v>502</v>
-      </c>
-      <c r="E477" t="n">
-        <v>5</v>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D478" t="n">
-        <v>502</v>
-      </c>
-      <c r="E478" t="n">
-        <v>5</v>
-      </c>
-      <c r="F478" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:17</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C479" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D479" t="n">
-        <v>502</v>
-      </c>
-      <c r="E479" t="n">
-        <v>5</v>
-      </c>
-      <c r="F479" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B480" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C480" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D480" t="n">
-        <v>502</v>
-      </c>
-      <c r="E480" t="n">
-        <v>5</v>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B481" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C481" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D481" t="n">
-        <v>502</v>
-      </c>
-      <c r="E481" t="n">
-        <v>5</v>
-      </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D482" t="n">
-        <v>502</v>
-      </c>
-      <c r="E482" t="n">
-        <v>5</v>
-      </c>
-      <c r="F482" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B483" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D483" t="n">
-        <v>502</v>
-      </c>
-      <c r="E483" t="n">
-        <v>5</v>
-      </c>
-      <c r="F483" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:10:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D484" t="n">
-        <v>502</v>
-      </c>
-      <c r="E484" t="n">
-        <v>5</v>
-      </c>
-      <c r="F484" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D485" t="n">
-        <v>502</v>
-      </c>
-      <c r="E485" t="n">
-        <v>5</v>
-      </c>
-      <c r="F485" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D486" t="n">
-        <v>502</v>
-      </c>
-      <c r="E486" t="n">
-        <v>5</v>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:23</t>
-        </is>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B487" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D487" t="n">
-        <v>502</v>
-      </c>
-      <c r="E487" t="n">
-        <v>5</v>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:31</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F783FC88A5B43B776A9B015CBD8D2C27?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D488" t="n">
-        <v>502</v>
-      </c>
-      <c r="E488" t="n">
-        <v>5</v>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D489" t="n">
-        <v>502</v>
-      </c>
-      <c r="E489" t="n">
-        <v>5</v>
-      </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:48</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D490" t="n">
-        <v>502</v>
-      </c>
-      <c r="E490" t="n">
-        <v>5</v>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:11:56</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D491" t="n">
-        <v>502</v>
-      </c>
-      <c r="E491" t="n">
-        <v>5</v>
-      </c>
-      <c r="F491" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B492" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D492" t="n">
-        <v>502</v>
-      </c>
-      <c r="E492" t="n">
-        <v>5</v>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B493" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D493" t="n">
-        <v>502</v>
-      </c>
-      <c r="E493" t="n">
-        <v>5</v>
-      </c>
-      <c r="F493" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B494" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D494" t="n">
-        <v>502</v>
-      </c>
-      <c r="E494" t="n">
-        <v>5</v>
-      </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:29</t>
-        </is>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B495" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D495" t="n">
-        <v>502</v>
-      </c>
-      <c r="E495" t="n">
-        <v>5</v>
-      </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D496" t="n">
-        <v>502</v>
-      </c>
-      <c r="E496" t="n">
-        <v>5</v>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B497" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D497" t="n">
-        <v>502</v>
-      </c>
-      <c r="E497" t="n">
-        <v>5</v>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:12:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B498" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D498" t="n">
-        <v>502</v>
-      </c>
-      <c r="E498" t="n">
-        <v>5</v>
-      </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B499" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D499" t="n">
-        <v>502</v>
-      </c>
-      <c r="E499" t="n">
-        <v>5</v>
-      </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B500" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D500" t="n">
-        <v>502</v>
-      </c>
-      <c r="E500" t="n">
-        <v>5</v>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B501" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D501" t="n">
-        <v>502</v>
-      </c>
-      <c r="E501" t="n">
-        <v>5</v>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:26</t>
-        </is>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B502" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D502" t="n">
-        <v>502</v>
-      </c>
-      <c r="E502" t="n">
-        <v>5</v>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B503" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D503" t="n">
-        <v>502</v>
-      </c>
-      <c r="E503" t="n">
-        <v>5</v>
-      </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DC246BFCFB90397A27924A32DC6EC315?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D504" t="n">
-        <v>502</v>
-      </c>
-      <c r="E504" t="n">
-        <v>5</v>
-      </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B505" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D505" t="n">
-        <v>502</v>
-      </c>
-      <c r="E505" t="n">
-        <v>5</v>
-      </c>
-      <c r="F505" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:13:59</t>
-        </is>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B506" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D506" t="n">
-        <v>502</v>
-      </c>
-      <c r="E506" t="n">
-        <v>5</v>
-      </c>
-      <c r="F506" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B507" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>502</v>
-      </c>
-      <c r="E507" t="n">
-        <v>5</v>
-      </c>
-      <c r="F507" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:16</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B508" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>502</v>
-      </c>
-      <c r="E508" t="n">
-        <v>5</v>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>502</v>
-      </c>
-      <c r="E509" t="n">
-        <v>5</v>
-      </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B510" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>502</v>
-      </c>
-      <c r="E510" t="n">
-        <v>5</v>
-      </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:40</t>
-        </is>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B511" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>502</v>
-      </c>
-      <c r="E511" t="n">
-        <v>5</v>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B512" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>502</v>
-      </c>
-      <c r="E512" t="n">
-        <v>5</v>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:14:57</t>
-        </is>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B513" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>502</v>
-      </c>
-      <c r="E513" t="n">
-        <v>5</v>
-      </c>
-      <c r="F513" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:05</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B514" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>502</v>
-      </c>
-      <c r="E514" t="n">
-        <v>5</v>
-      </c>
-      <c r="F514" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:13</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D515" t="n">
-        <v>502</v>
-      </c>
-      <c r="E515" t="n">
-        <v>5</v>
-      </c>
-      <c r="F515" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D516" t="n">
-        <v>502</v>
-      </c>
-      <c r="E516" t="n">
-        <v>5</v>
-      </c>
-      <c r="F516" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D517" t="n">
-        <v>502</v>
-      </c>
-      <c r="E517" t="n">
-        <v>5</v>
-      </c>
-      <c r="F517" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:38</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B518" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D518" t="n">
-        <v>502</v>
-      </c>
-      <c r="E518" t="n">
-        <v>5</v>
-      </c>
-      <c r="F518" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B519" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D519" t="n">
-        <v>502</v>
-      </c>
-      <c r="E519" t="n">
-        <v>5</v>
-      </c>
-      <c r="F519" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:15:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA89F153D53C66DB8BE7CE740BC6B800?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D520" t="n">
-        <v>502</v>
-      </c>
-      <c r="E520" t="n">
-        <v>5</v>
-      </c>
-      <c r="F520" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D521" t="n">
-        <v>502</v>
-      </c>
-      <c r="E521" t="n">
-        <v>5</v>
-      </c>
-      <c r="F521" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B522" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D522" t="n">
-        <v>502</v>
-      </c>
-      <c r="E522" t="n">
-        <v>5</v>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B523" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D523" t="n">
-        <v>502</v>
-      </c>
-      <c r="E523" t="n">
-        <v>5</v>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B524" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D524" t="n">
-        <v>502</v>
-      </c>
-      <c r="E524" t="n">
-        <v>5</v>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:35</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D525" t="n">
-        <v>502</v>
-      </c>
-      <c r="E525" t="n">
-        <v>5</v>
-      </c>
-      <c r="F525" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B526" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D526" t="n">
-        <v>502</v>
-      </c>
-      <c r="E526" t="n">
-        <v>5</v>
-      </c>
-      <c r="F526" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:16:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B527" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>HTTP_502</t>
-        </is>
-      </c>
-      <c r="D527" t="n">
-        <v>502</v>
-      </c>
-      <c r="E527" t="n">
-        <v>5</v>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:17:01</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D528" t="n">
-        <v>0</v>
-      </c>
-      <c r="E528" t="n">
-        <v>5</v>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:17:58</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>0</v>
-      </c>
-      <c r="E529" t="n">
-        <v>5</v>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:19:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>0</v>
-      </c>
-      <c r="E530" t="n">
-        <v>5</v>
-      </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:20:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B531" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>0</v>
-      </c>
-      <c r="E531" t="n">
-        <v>5</v>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:22:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>abatia</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9E15F6C0AF1D404A662111CD57966F79?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
-        </is>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>0</v>
-      </c>
-      <c r="E532" t="n">
-        <v>5</v>
-      </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>2026-07-30 07:23:41</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F388"/>
+  <dimension ref="A1:F451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11284,6 +11284,1770 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=00CDF12EB8D3827634D79C05009B0FE1?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>0</v>
+      </c>
+      <c r="E389" t="n">
+        <v>6</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:57:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=19E48E5593B51B8203CFF5A29E206288?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>0</v>
+      </c>
+      <c r="E390" t="n">
+        <v>6</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:01:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1DB0E756E1C061D09AAF974F1B434815?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
+        <v>0</v>
+      </c>
+      <c r="E391" t="n">
+        <v>6</v>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:02:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DDCE7B8A1B7D2EEB88A1D472B3B244A0?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>0</v>
+      </c>
+      <c r="E392" t="n">
+        <v>6</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A1B48967BAF8E1A635EEFDA5BA9E6EDE?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=SETEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>0</v>
+      </c>
+      <c r="E393" t="n">
+        <v>6</v>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:17:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=2B708D2A1E30C8C83D8A666ABB166ED6?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>0</v>
+      </c>
+      <c r="E394" t="n">
+        <v>6</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:20:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=3D5D88D14E91F9444A6F30EE76BE5162?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>0</v>
+      </c>
+      <c r="E395" t="n">
+        <v>6</v>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:24:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=031CE6644B7B7A86C78BCD00EC265964?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>0</v>
+      </c>
+      <c r="E396" t="n">
+        <v>6</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:25:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A1EEB9106F51B21BE7BFC2F64846356D?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>0</v>
+      </c>
+      <c r="E397" t="n">
+        <v>6</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:27:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6FBC8CA7C2924E7F7B566C80341B27A5?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>0</v>
+      </c>
+      <c r="E398" t="n">
+        <v>6</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:29:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=11C4EF694DFF3D359586E6EE0B46155E?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>0</v>
+      </c>
+      <c r="E399" t="n">
+        <v>6</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:30:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5748551C0F41482D845FC54E70424F07?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>0</v>
+      </c>
+      <c r="E400" t="n">
+        <v>6</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:33:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6C8330313B889778B1CED8FF1AF4F1B6?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>0</v>
+      </c>
+      <c r="E401" t="n">
+        <v>6</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:34:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=2C891E4E5E8CFAAC6F35535328C8597E?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
+      </c>
+      <c r="E402" t="n">
+        <v>6</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:34:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4B68EFAD66F280E3B7F72BA7492696E5?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
+      </c>
+      <c r="E403" t="n">
+        <v>6</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:38:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=914D4CD203ED6AAC8189DABAD1CCC7E1?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>0</v>
+      </c>
+      <c r="E404" t="n">
+        <v>6</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:39:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1F51CA6EF2BEEDEB953F3B8C8AFBC8AE?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>0</v>
+      </c>
+      <c r="E405" t="n">
+        <v>6</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:40:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=FF14E97F6367793E64A77A1DCAC2A723?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>0</v>
+      </c>
+      <c r="E406" t="n">
+        <v>6</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:41:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=2&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>0</v>
+      </c>
+      <c r="E407" t="n">
+        <v>6</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=2&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
+      </c>
+      <c r="E408" t="n">
+        <v>6</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=5&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>0</v>
+      </c>
+      <c r="E409" t="n">
+        <v>6</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=5&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>0</v>
+      </c>
+      <c r="E410" t="n">
+        <v>6</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=6&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>0</v>
+      </c>
+      <c r="E411" t="n">
+        <v>6</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=6&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>0</v>
+      </c>
+      <c r="E412" t="n">
+        <v>6</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>0</v>
+      </c>
+      <c r="E413" t="n">
+        <v>6</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DD04C372CBF4B7BA194C4B02E7B2417F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>0</v>
+      </c>
+      <c r="E414" t="n">
+        <v>6</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:43:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=82A7F1F8C0C6EFDAC7CC73B35084CD60?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>0</v>
+      </c>
+      <c r="E415" t="n">
+        <v>6</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:44:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=1&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>0</v>
+      </c>
+      <c r="E416" t="n">
+        <v>6</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:45:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=1&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>0</v>
+      </c>
+      <c r="E417" t="n">
+        <v>6</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=2&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" t="n">
+        <v>6</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:45:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=2&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" t="n">
+        <v>6</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:45:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0</v>
+      </c>
+      <c r="E420" t="n">
+        <v>6</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:46:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>0</v>
+      </c>
+      <c r="E421" t="n">
+        <v>6</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=75C9657509AD83D7ACED45763BE2A976?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=10&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>0</v>
+      </c>
+      <c r="E422" t="n">
+        <v>6</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:46:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5B499ADAF587097CDE08F70729538AA6?d-5470-p=4&amp;formulario.exercicio=2020&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0</v>
+      </c>
+      <c r="E423" t="n">
+        <v>6</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:47:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5B499ADAF587097CDE08F70729538AA6?d-5470-p=4&amp;formulario.exercicio=2020&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" t="n">
+        <v>6</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:47:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5B499ADAF587097CDE08F70729538AA6?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>0</v>
+      </c>
+      <c r="E425" t="n">
+        <v>6</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:47:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=83C9119E917F1546C67CDF011D51654D?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>0</v>
+      </c>
+      <c r="E426" t="n">
+        <v>6</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:48:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=878E5C91B0B20A2CF304DBC6082946EB?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>0</v>
+      </c>
+      <c r="E427" t="n">
+        <v>6</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:50:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=95801FFDA2EADE807BFF13578096A695?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>0</v>
+      </c>
+      <c r="E428" t="n">
+        <v>6</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:51:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=354578055FFE8964BEBE7E7A0CAA447D?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" t="n">
+        <v>6</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:52:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9908FD8AA7E2A23E3F4790C841C88588?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>0</v>
+      </c>
+      <c r="E430" t="n">
+        <v>6</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:53:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C6B40012BEA5C5A631F44DD549E6E422?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>0</v>
+      </c>
+      <c r="E431" t="n">
+        <v>6</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5EFB7D6BF60A98EEE9F115E1D24D73B1?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>0</v>
+      </c>
+      <c r="E432" t="n">
+        <v>6</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>2026-07-31 23:54:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=B1A5861BC5B9CE4C2AC5091151826F8E?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>0</v>
+      </c>
+      <c r="E433" t="n">
+        <v>6</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:00:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CEBFE38EB8AAFA7E61C60AA13BB144FC?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" t="n">
+        <v>6</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:01:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BA60F01DB9DBCA80DC4BAF2B3EDA2A18?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="n">
+        <v>6</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:02:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E98D9136531BE17BE2011A91112CBDC9?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2020&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>0</v>
+      </c>
+      <c r="E436" t="n">
+        <v>6</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:05:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=23B51764A9B17D808E223CE425118D56?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>0</v>
+      </c>
+      <c r="E437" t="n">
+        <v>6</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=7616D65F64398860BCB4AB2FB0905D2E?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>0</v>
+      </c>
+      <c r="E438" t="n">
+        <v>6</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:14:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=2D8451D91E6CA50CE43B59F0C8B6CE93?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>0</v>
+      </c>
+      <c r="E439" t="n">
+        <v>6</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0C58E2E330E3B747394F6FD884C8171F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>0</v>
+      </c>
+      <c r="E440" t="n">
+        <v>6</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=8B91EC1B046070D6C3DA1DC26C5D547C?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="n">
+        <v>6</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:44:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5BEC913BCBF509C7B9A040EE6C6F3DD7?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>0</v>
+      </c>
+      <c r="E442" t="n">
+        <v>6</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:06:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=20FEB724BE11931BB119C96D158502AE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>0</v>
+      </c>
+      <c r="E443" t="n">
+        <v>6</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:17:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=7A3A6C91150B94CED6924267C3448436?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>0</v>
+      </c>
+      <c r="E444" t="n">
+        <v>6</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:23:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=778500C98514E3A75A9431A66EC9B34F?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>0</v>
+      </c>
+      <c r="E445" t="n">
+        <v>6</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:33:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E6E7B396A9C6830DD6F1806C93D51629?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>0</v>
+      </c>
+      <c r="E446" t="n">
+        <v>6</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:36:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=216F0B6504C010322EDAD195304D9F0F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>0</v>
+      </c>
+      <c r="E447" t="n">
+        <v>6</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:39:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A6281B5E63B4C32D032C7F8B68DA9D14?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>0</v>
+      </c>
+      <c r="E448" t="n">
+        <v>6</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:56:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=56494504DC7D61CC7B1F77BE24BFDA9D?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>0</v>
+      </c>
+      <c r="E449" t="n">
+        <v>6</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:57:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0D1AA412DE062F7FB61F2894EBA7765B?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>0</v>
+      </c>
+      <c r="E450" t="n">
+        <v>6</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>2026-08-01 02:24:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6A5B5DF6686147B93D7869EC8DFBA619?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2019&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>0</v>
+      </c>
+      <c r="E451" t="n">
+        <v>6</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-08-01 02:26:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:F454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13048,6 +13048,90 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0AFDD41E7625530CEED7199BE7C00B41?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2016&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>0</v>
+      </c>
+      <c r="E452" t="n">
+        <v>6</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-08-01 13:16:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C7C1FE45559E3058EB96AE42F9038A26?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>0</v>
+      </c>
+      <c r="E453" t="n">
+        <v>6</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-08-01 13:48:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=7ADBCE5A8DD1BFFEC64A6AF59A4890C5?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=ABRIL&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>6</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-08-01 15:35:23</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F454"/>
+  <dimension ref="A1:F733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13132,6 +13132,7818 @@
         </is>
       </c>
     </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=191A06687DD172B8BC4E266CE025EFF2?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>0</v>
+      </c>
+      <c r="E455" t="n">
+        <v>6</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:08:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=B253E0C2E68AA107BF2E34AAF25AEEEF?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>6</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AB592BC82382BBE01293449081173E97?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>0</v>
+      </c>
+      <c r="E457" t="n">
+        <v>6</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:19:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AF1A8284089A00D092C75472F1789228?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>6</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:23:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1D62DB3A05E9FE59C6141CDD811165E2?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>0</v>
+      </c>
+      <c r="E459" t="n">
+        <v>6</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:36:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AC1CEE3F53C34D616859260CE7FD64D2?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>6</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-08-01 22:43:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4B4F56416F79E1BA4BE81FD1203404FD?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>0</v>
+      </c>
+      <c r="E461" t="n">
+        <v>6</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:20:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D27BCFD2B96C3E4BBDE5F5A0C64C9025?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>6</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:29:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9C7DCEC49AE458A9EF073CBCC76E82D2?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>0</v>
+      </c>
+      <c r="E463" t="n">
+        <v>6</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E3227FA95798C2F9875C920F88ACF2E2?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=NOVEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>6</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-08-01 23:58:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4B1F6EE5A04F7EF746425365C5012956?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>0</v>
+      </c>
+      <c r="E465" t="n">
+        <v>6</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:01:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=854590F6A538FF7857FDB8A301F7B801?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>6</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:13:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=FF9487A465F1459173C1146BB955FAFE?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>0</v>
+      </c>
+      <c r="E467" t="n">
+        <v>6</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1DE8082A5703F0DB83FA8E17D7C3E917?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>6</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:19:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1FF5B07329DC16C57B77E9E6D367C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2014&amp;d-5470-e=9&amp;formulario.mes=DEZEMBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>0</v>
+      </c>
+      <c r="E469" t="n">
+        <v>6</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:23:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1317364A873CD69F71A313F178ABFCBD?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>0</v>
+      </c>
+      <c r="E470" t="n">
+        <v>6</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:24:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9D38DF644BCF49FE97A828F23DA3460E?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>0</v>
+      </c>
+      <c r="E471" t="n">
+        <v>6</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D45EC039840824FC51BBD10691F56B2E?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>6</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:34:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F0AA5A591ECE969B18E64BE5C4E9F757?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>0</v>
+      </c>
+      <c r="E473" t="n">
+        <v>6</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-08-02 00:35:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=648472441240CF200CC8743B56979856?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>0</v>
+      </c>
+      <c r="E474" t="n">
+        <v>6</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:05:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=3157C044E64B1585C6191D5CB49DE4FD?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>0</v>
+      </c>
+      <c r="E475" t="n">
+        <v>6</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:18:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=8DDBD594082723B5872A29F1585AF39D?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>6</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:19:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=65A233B9029BFBE74D975DCE53064272?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>0</v>
+      </c>
+      <c r="E477" t="n">
+        <v>6</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1E53367E006E6150263B47BAE3E392B8?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>6</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:27:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6CDEE3160CD3640EEFA1FF77D1A155DC?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>0</v>
+      </c>
+      <c r="E479" t="n">
+        <v>6</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:30:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5EF00073D699951E6BAC0111540B3EB5?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>6</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-08-02 01:32:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=8C17CB9472A7F81D0754B535CF8E1FEE?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>0</v>
+      </c>
+      <c r="E481" t="n">
+        <v>7</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-08-02 21:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=F9CEE04EEDAA504EC82D2902E5C52B29?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>7</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:04:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C11F3318590AA1E8EA4583BFB90229A0?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>0</v>
+      </c>
+      <c r="E483" t="n">
+        <v>7</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:07:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=39BCAEB5A93DD17BE8E0CE5F51A82A12?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>7</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:24:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=7908CB8D9A0518BE74A37527F4FE7048?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>0</v>
+      </c>
+      <c r="E485" t="n">
+        <v>7</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:32:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=925753FAE0191EF5165C09015B975182?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>7</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:37:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=865411FCB083F5267F2CF4C305EC60C5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>0</v>
+      </c>
+      <c r="E487" t="n">
+        <v>7</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-08-03 02:40:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=458CE4D19E07091FB47479CF9B9949A3?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>7</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:11:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32FEF149ADE66CBE60D60008D1ACD6FE?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>0</v>
+      </c>
+      <c r="E489" t="n">
+        <v>7</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0F2985D6253F7D4C843A61E5AF3A6657?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
+      <c r="E490" t="n">
+        <v>7</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:16:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=B1FDC22539CB0BDD288FF7C992FEEA05?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>7</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=3106FD522674EDAC89D4888A9A4267CD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>7</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:23:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=22C72C71B88C77508869B904F04B8EFD?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
+        <v>7</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:26:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=63F50860924E7EB8CBB181ABC3B46524?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>7</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:27:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=3E6416BA609C12AAC0B0CE7D4A3D236B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>0</v>
+      </c>
+      <c r="E495" t="n">
+        <v>7</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:28:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A1300FE3E7DB6FB2D3017FE4312CB737?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>7</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:32:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AD26ABAF663C53F18B1A99D71C021B12?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>0</v>
+      </c>
+      <c r="E497" t="n">
+        <v>7</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=860BFDE7A307550F89D77B36F749C182?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>7</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:38:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=368AE8C25D760CAA1D7E35FD946CE292?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>0</v>
+      </c>
+      <c r="E499" t="n">
+        <v>7</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:44:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4C10629964C4597132C9C1C943F18F7B?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>0</v>
+      </c>
+      <c r="E500" t="n">
+        <v>7</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:45:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=2E22E4C725ED977E87D634B3C46A2B0C?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>0</v>
+      </c>
+      <c r="E501" t="n">
+        <v>7</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:47:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=1156E98D12B6B8F73514E7F62D73CD16?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>7</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:49:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0E41A19704C7777AFACAF7E7CF520E85?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2026&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>0</v>
+      </c>
+      <c r="E503" t="n">
+        <v>7</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:51:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>502</v>
+      </c>
+      <c r="E504" t="n">
+        <v>7</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:10:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>502</v>
+      </c>
+      <c r="E505" t="n">
+        <v>7</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>502</v>
+      </c>
+      <c r="E506" t="n">
+        <v>7</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:11:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>502</v>
+      </c>
+      <c r="E507" t="n">
+        <v>7</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:11:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>502</v>
+      </c>
+      <c r="E508" t="n">
+        <v>7</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:12:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>502</v>
+      </c>
+      <c r="E509" t="n">
+        <v>7</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>502</v>
+      </c>
+      <c r="E510" t="n">
+        <v>7</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:12:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>502</v>
+      </c>
+      <c r="E511" t="n">
+        <v>7</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:13:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>502</v>
+      </c>
+      <c r="E512" t="n">
+        <v>7</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:13:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>502</v>
+      </c>
+      <c r="E513" t="n">
+        <v>7</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:13:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>502</v>
+      </c>
+      <c r="E514" t="n">
+        <v>7</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:13:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>502</v>
+      </c>
+      <c r="E515" t="n">
+        <v>7</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:14:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=622360C0BEF51DF82F0D604507062303?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>502</v>
+      </c>
+      <c r="E516" t="n">
+        <v>7</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:14:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>502</v>
+      </c>
+      <c r="E517" t="n">
+        <v>7</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:14:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>502</v>
+      </c>
+      <c r="E518" t="n">
+        <v>7</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>502</v>
+      </c>
+      <c r="E519" t="n">
+        <v>7</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:15:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>502</v>
+      </c>
+      <c r="E520" t="n">
+        <v>7</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>502</v>
+      </c>
+      <c r="E521" t="n">
+        <v>7</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>502</v>
+      </c>
+      <c r="E522" t="n">
+        <v>7</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:15:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>502</v>
+      </c>
+      <c r="E523" t="n">
+        <v>7</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:16:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>502</v>
+      </c>
+      <c r="E524" t="n">
+        <v>7</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:16:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>502</v>
+      </c>
+      <c r="E525" t="n">
+        <v>7</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:16:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>502</v>
+      </c>
+      <c r="E526" t="n">
+        <v>7</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:16:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>502</v>
+      </c>
+      <c r="E527" t="n">
+        <v>7</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:17:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>502</v>
+      </c>
+      <c r="E528" t="n">
+        <v>7</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:17:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>502</v>
+      </c>
+      <c r="E529" t="n">
+        <v>7</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:17:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>502</v>
+      </c>
+      <c r="E530" t="n">
+        <v>7</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:18:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>502</v>
+      </c>
+      <c r="E531" t="n">
+        <v>7</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:18:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=5CACBB1B75630F5E436586D08C428616?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>502</v>
+      </c>
+      <c r="E532" t="n">
+        <v>7</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>502</v>
+      </c>
+      <c r="E533" t="n">
+        <v>7</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:18:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>502</v>
+      </c>
+      <c r="E534" t="n">
+        <v>7</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:19:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>502</v>
+      </c>
+      <c r="E535" t="n">
+        <v>7</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:19:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>502</v>
+      </c>
+      <c r="E536" t="n">
+        <v>7</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:19:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>502</v>
+      </c>
+      <c r="E537" t="n">
+        <v>7</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>502</v>
+      </c>
+      <c r="E538" t="n">
+        <v>7</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:20:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>502</v>
+      </c>
+      <c r="E539" t="n">
+        <v>7</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:20:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>502</v>
+      </c>
+      <c r="E540" t="n">
+        <v>7</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:20:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>502</v>
+      </c>
+      <c r="E541" t="n">
+        <v>7</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:21:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>502</v>
+      </c>
+      <c r="E542" t="n">
+        <v>7</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>502</v>
+      </c>
+      <c r="E543" t="n">
+        <v>7</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>502</v>
+      </c>
+      <c r="E544" t="n">
+        <v>7</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:21:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>502</v>
+      </c>
+      <c r="E545" t="n">
+        <v>7</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:22:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>502</v>
+      </c>
+      <c r="E546" t="n">
+        <v>7</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:22:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>502</v>
+      </c>
+      <c r="E547" t="n">
+        <v>7</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:23:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=33C7C879A786B7DD1BE8F6843A8C0DBB?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>502</v>
+      </c>
+      <c r="E548" t="n">
+        <v>7</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>502</v>
+      </c>
+      <c r="E549" t="n">
+        <v>7</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>502</v>
+      </c>
+      <c r="E550" t="n">
+        <v>7</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:24:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>502</v>
+      </c>
+      <c r="E551" t="n">
+        <v>7</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:25:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>502</v>
+      </c>
+      <c r="E552" t="n">
+        <v>7</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:25:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>502</v>
+      </c>
+      <c r="E553" t="n">
+        <v>7</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>502</v>
+      </c>
+      <c r="E554" t="n">
+        <v>7</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:26:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>502</v>
+      </c>
+      <c r="E555" t="n">
+        <v>7</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>502</v>
+      </c>
+      <c r="E556" t="n">
+        <v>7</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>502</v>
+      </c>
+      <c r="E557" t="n">
+        <v>7</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:27:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>502</v>
+      </c>
+      <c r="E558" t="n">
+        <v>7</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:27:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>502</v>
+      </c>
+      <c r="E559" t="n">
+        <v>7</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:28:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>502</v>
+      </c>
+      <c r="E560" t="n">
+        <v>7</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:28:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>502</v>
+      </c>
+      <c r="E561" t="n">
+        <v>7</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:28:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>502</v>
+      </c>
+      <c r="E562" t="n">
+        <v>7</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:29:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>502</v>
+      </c>
+      <c r="E563" t="n">
+        <v>7</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=353CD86373B455772E66C2A9117C34BF?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>502</v>
+      </c>
+      <c r="E564" t="n">
+        <v>7</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:30:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>502</v>
+      </c>
+      <c r="E565" t="n">
+        <v>7</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:30:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>502</v>
+      </c>
+      <c r="E566" t="n">
+        <v>7</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:30:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>502</v>
+      </c>
+      <c r="E567" t="n">
+        <v>7</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:31:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>502</v>
+      </c>
+      <c r="E568" t="n">
+        <v>7</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:31:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>502</v>
+      </c>
+      <c r="E569" t="n">
+        <v>7</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:32:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>502</v>
+      </c>
+      <c r="E570" t="n">
+        <v>7</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:32:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>502</v>
+      </c>
+      <c r="E571" t="n">
+        <v>7</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:33:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>502</v>
+      </c>
+      <c r="E572" t="n">
+        <v>7</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>502</v>
+      </c>
+      <c r="E573" t="n">
+        <v>7</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:33:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>502</v>
+      </c>
+      <c r="E574" t="n">
+        <v>7</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:34:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>502</v>
+      </c>
+      <c r="E575" t="n">
+        <v>7</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:34:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>502</v>
+      </c>
+      <c r="E576" t="n">
+        <v>7</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:34:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>502</v>
+      </c>
+      <c r="E577" t="n">
+        <v>7</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:35:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>502</v>
+      </c>
+      <c r="E578" t="n">
+        <v>7</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:35:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>502</v>
+      </c>
+      <c r="E579" t="n">
+        <v>7</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:36:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A4233C006003D9582949B6590514ADB5?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>502</v>
+      </c>
+      <c r="E580" t="n">
+        <v>7</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:36:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>502</v>
+      </c>
+      <c r="E581" t="n">
+        <v>7</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:37:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>502</v>
+      </c>
+      <c r="E582" t="n">
+        <v>7</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:37:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>502</v>
+      </c>
+      <c r="E583" t="n">
+        <v>7</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>502</v>
+      </c>
+      <c r="E584" t="n">
+        <v>7</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>502</v>
+      </c>
+      <c r="E585" t="n">
+        <v>7</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:38:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>502</v>
+      </c>
+      <c r="E586" t="n">
+        <v>7</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:38:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>502</v>
+      </c>
+      <c r="E587" t="n">
+        <v>7</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:39:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>502</v>
+      </c>
+      <c r="E588" t="n">
+        <v>7</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:40:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>502</v>
+      </c>
+      <c r="E589" t="n">
+        <v>7</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>502</v>
+      </c>
+      <c r="E590" t="n">
+        <v>7</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:40:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>502</v>
+      </c>
+      <c r="E591" t="n">
+        <v>7</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:40:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>502</v>
+      </c>
+      <c r="E592" t="n">
+        <v>7</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>502</v>
+      </c>
+      <c r="E593" t="n">
+        <v>7</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:41:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>502</v>
+      </c>
+      <c r="E594" t="n">
+        <v>7</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:41:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>502</v>
+      </c>
+      <c r="E595" t="n">
+        <v>7</v>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:42:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D74F9EB2B3ECEFEE2F2734B89F3D6320?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>502</v>
+      </c>
+      <c r="E596" t="n">
+        <v>7</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:43:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>502</v>
+      </c>
+      <c r="E597" t="n">
+        <v>7</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:43:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>502</v>
+      </c>
+      <c r="E598" t="n">
+        <v>7</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:43:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>502</v>
+      </c>
+      <c r="E599" t="n">
+        <v>7</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:44:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>502</v>
+      </c>
+      <c r="E600" t="n">
+        <v>7</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:44:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>502</v>
+      </c>
+      <c r="E601" t="n">
+        <v>7</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:44:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>502</v>
+      </c>
+      <c r="E602" t="n">
+        <v>7</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:45:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>502</v>
+      </c>
+      <c r="E603" t="n">
+        <v>7</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:45:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>502</v>
+      </c>
+      <c r="E604" t="n">
+        <v>7</v>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:46:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>502</v>
+      </c>
+      <c r="E605" t="n">
+        <v>7</v>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:46:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>502</v>
+      </c>
+      <c r="E606" t="n">
+        <v>7</v>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:47:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>502</v>
+      </c>
+      <c r="E607" t="n">
+        <v>7</v>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:47:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>502</v>
+      </c>
+      <c r="E608" t="n">
+        <v>7</v>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:47:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>502</v>
+      </c>
+      <c r="E609" t="n">
+        <v>7</v>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:48:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>502</v>
+      </c>
+      <c r="E610" t="n">
+        <v>7</v>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:48:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>502</v>
+      </c>
+      <c r="E611" t="n">
+        <v>7</v>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:49:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=32D9B3453C5C051300239C57031D5880?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>502</v>
+      </c>
+      <c r="E612" t="n">
+        <v>7</v>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:49:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>502</v>
+      </c>
+      <c r="E613" t="n">
+        <v>7</v>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:50:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>502</v>
+      </c>
+      <c r="E614" t="n">
+        <v>7</v>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:50:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>502</v>
+      </c>
+      <c r="E615" t="n">
+        <v>7</v>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:50:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>502</v>
+      </c>
+      <c r="E616" t="n">
+        <v>7</v>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:51:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>502</v>
+      </c>
+      <c r="E617" t="n">
+        <v>7</v>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:51:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>502</v>
+      </c>
+      <c r="E618" t="n">
+        <v>7</v>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:51:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>502</v>
+      </c>
+      <c r="E619" t="n">
+        <v>7</v>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:52:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>502</v>
+      </c>
+      <c r="E620" t="n">
+        <v>7</v>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:52:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>502</v>
+      </c>
+      <c r="E621" t="n">
+        <v>7</v>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:53:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>502</v>
+      </c>
+      <c r="E622" t="n">
+        <v>7</v>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:53:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>502</v>
+      </c>
+      <c r="E623" t="n">
+        <v>7</v>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:54:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>502</v>
+      </c>
+      <c r="E624" t="n">
+        <v>7</v>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:54:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>502</v>
+      </c>
+      <c r="E625" t="n">
+        <v>7</v>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:54:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>502</v>
+      </c>
+      <c r="E626" t="n">
+        <v>7</v>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:55:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>502</v>
+      </c>
+      <c r="E627" t="n">
+        <v>7</v>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:55:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D4CB38DB98F0EADAE2282530DE4A29F9?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>502</v>
+      </c>
+      <c r="E628" t="n">
+        <v>7</v>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:55:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>502</v>
+      </c>
+      <c r="E629" t="n">
+        <v>7</v>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:56:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>502</v>
+      </c>
+      <c r="E630" t="n">
+        <v>7</v>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:56:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>502</v>
+      </c>
+      <c r="E631" t="n">
+        <v>7</v>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:57:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>502</v>
+      </c>
+      <c r="E632" t="n">
+        <v>7</v>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:57:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>502</v>
+      </c>
+      <c r="E633" t="n">
+        <v>7</v>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:58:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>502</v>
+      </c>
+      <c r="E634" t="n">
+        <v>7</v>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:58:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>502</v>
+      </c>
+      <c r="E635" t="n">
+        <v>7</v>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:59:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>502</v>
+      </c>
+      <c r="E636" t="n">
+        <v>7</v>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026-08-03 07:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>502</v>
+      </c>
+      <c r="E637" t="n">
+        <v>7</v>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>502</v>
+      </c>
+      <c r="E638" t="n">
+        <v>7</v>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:00:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>502</v>
+      </c>
+      <c r="E639" t="n">
+        <v>7</v>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:01:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>502</v>
+      </c>
+      <c r="E640" t="n">
+        <v>7</v>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:01:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>502</v>
+      </c>
+      <c r="E641" t="n">
+        <v>7</v>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:01:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>502</v>
+      </c>
+      <c r="E642" t="n">
+        <v>7</v>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:02:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>502</v>
+      </c>
+      <c r="E643" t="n">
+        <v>7</v>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:02:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C54126E3BAB1EDCA46C669DA6A443F4A?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>502</v>
+      </c>
+      <c r="E644" t="n">
+        <v>7</v>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:03:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>502</v>
+      </c>
+      <c r="E645" t="n">
+        <v>7</v>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:03:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>502</v>
+      </c>
+      <c r="E646" t="n">
+        <v>7</v>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:03:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>502</v>
+      </c>
+      <c r="E647" t="n">
+        <v>7</v>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:04:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>502</v>
+      </c>
+      <c r="E648" t="n">
+        <v>7</v>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:04:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>502</v>
+      </c>
+      <c r="E649" t="n">
+        <v>7</v>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:05:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>502</v>
+      </c>
+      <c r="E650" t="n">
+        <v>7</v>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:05:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>502</v>
+      </c>
+      <c r="E651" t="n">
+        <v>7</v>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:05:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>502</v>
+      </c>
+      <c r="E652" t="n">
+        <v>7</v>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:06:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>502</v>
+      </c>
+      <c r="E653" t="n">
+        <v>7</v>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:06:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>502</v>
+      </c>
+      <c r="E654" t="n">
+        <v>7</v>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:06:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>502</v>
+      </c>
+      <c r="E655" t="n">
+        <v>7</v>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:07:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>502</v>
+      </c>
+      <c r="E656" t="n">
+        <v>7</v>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>502</v>
+      </c>
+      <c r="E657" t="n">
+        <v>7</v>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:08:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>502</v>
+      </c>
+      <c r="E658" t="n">
+        <v>7</v>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:08:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>502</v>
+      </c>
+      <c r="E659" t="n">
+        <v>7</v>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:08:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=A0E1D6A31C77D3C3A5A39BDA1411C0A3?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>502</v>
+      </c>
+      <c r="E660" t="n">
+        <v>7</v>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:08:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>502</v>
+      </c>
+      <c r="E661" t="n">
+        <v>7</v>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:09:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>502</v>
+      </c>
+      <c r="E662" t="n">
+        <v>7</v>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>502</v>
+      </c>
+      <c r="E663" t="n">
+        <v>7</v>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:09:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>502</v>
+      </c>
+      <c r="E664" t="n">
+        <v>7</v>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>502</v>
+      </c>
+      <c r="E665" t="n">
+        <v>7</v>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:10:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>502</v>
+      </c>
+      <c r="E666" t="n">
+        <v>7</v>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:11:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>502</v>
+      </c>
+      <c r="E667" t="n">
+        <v>7</v>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:11:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>502</v>
+      </c>
+      <c r="E668" t="n">
+        <v>7</v>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:11:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>502</v>
+      </c>
+      <c r="E669" t="n">
+        <v>7</v>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:12:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>502</v>
+      </c>
+      <c r="E670" t="n">
+        <v>7</v>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:12:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>502</v>
+      </c>
+      <c r="E671" t="n">
+        <v>7</v>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:13:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>502</v>
+      </c>
+      <c r="E672" t="n">
+        <v>7</v>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:13:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>502</v>
+      </c>
+      <c r="E673" t="n">
+        <v>7</v>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:14:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>502</v>
+      </c>
+      <c r="E674" t="n">
+        <v>7</v>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>502</v>
+      </c>
+      <c r="E675" t="n">
+        <v>7</v>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:15:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=D5CE43542A3DC01C74E2A97E7D0C1655?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>502</v>
+      </c>
+      <c r="E676" t="n">
+        <v>7</v>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:15:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>502</v>
+      </c>
+      <c r="E677" t="n">
+        <v>7</v>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>502</v>
+      </c>
+      <c r="E678" t="n">
+        <v>7</v>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:16:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>502</v>
+      </c>
+      <c r="E679" t="n">
+        <v>7</v>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:16:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>502</v>
+      </c>
+      <c r="E680" t="n">
+        <v>7</v>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>502</v>
+      </c>
+      <c r="E681" t="n">
+        <v>7</v>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:17:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>502</v>
+      </c>
+      <c r="E682" t="n">
+        <v>7</v>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:17:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>502</v>
+      </c>
+      <c r="E683" t="n">
+        <v>7</v>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>502</v>
+      </c>
+      <c r="E684" t="n">
+        <v>7</v>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>502</v>
+      </c>
+      <c r="E685" t="n">
+        <v>7</v>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:19:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>502</v>
+      </c>
+      <c r="E686" t="n">
+        <v>7</v>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:19:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>502</v>
+      </c>
+      <c r="E687" t="n">
+        <v>7</v>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:20:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>502</v>
+      </c>
+      <c r="E688" t="n">
+        <v>7</v>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:20:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>502</v>
+      </c>
+      <c r="E689" t="n">
+        <v>7</v>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:21:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>502</v>
+      </c>
+      <c r="E690" t="n">
+        <v>7</v>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>502</v>
+      </c>
+      <c r="E691" t="n">
+        <v>7</v>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=6E7F8557BEDA220EE9B2B284EC09D025?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>502</v>
+      </c>
+      <c r="E692" t="n">
+        <v>7</v>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>502</v>
+      </c>
+      <c r="E693" t="n">
+        <v>7</v>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>502</v>
+      </c>
+      <c r="E694" t="n">
+        <v>7</v>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:23:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>502</v>
+      </c>
+      <c r="E695" t="n">
+        <v>7</v>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:23:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>502</v>
+      </c>
+      <c r="E696" t="n">
+        <v>7</v>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:23:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>502</v>
+      </c>
+      <c r="E697" t="n">
+        <v>7</v>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:24:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>502</v>
+      </c>
+      <c r="E698" t="n">
+        <v>7</v>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:25:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>502</v>
+      </c>
+      <c r="E699" t="n">
+        <v>7</v>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:25:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>502</v>
+      </c>
+      <c r="E700" t="n">
+        <v>7</v>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:25:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>502</v>
+      </c>
+      <c r="E701" t="n">
+        <v>7</v>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:26:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>502</v>
+      </c>
+      <c r="E702" t="n">
+        <v>7</v>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:26:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>502</v>
+      </c>
+      <c r="E703" t="n">
+        <v>7</v>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:27:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>502</v>
+      </c>
+      <c r="E704" t="n">
+        <v>7</v>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:27:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>502</v>
+      </c>
+      <c r="E705" t="n">
+        <v>7</v>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:28:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>502</v>
+      </c>
+      <c r="E706" t="n">
+        <v>7</v>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:28:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>502</v>
+      </c>
+      <c r="E707" t="n">
+        <v>7</v>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4454C1F6531025549D183A8D1209B412?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>502</v>
+      </c>
+      <c r="E708" t="n">
+        <v>7</v>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:29:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>502</v>
+      </c>
+      <c r="E709" t="n">
+        <v>7</v>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:29:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>502</v>
+      </c>
+      <c r="E710" t="n">
+        <v>7</v>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:30:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>502</v>
+      </c>
+      <c r="E711" t="n">
+        <v>7</v>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:30:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>502</v>
+      </c>
+      <c r="E712" t="n">
+        <v>7</v>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:30:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>502</v>
+      </c>
+      <c r="E713" t="n">
+        <v>7</v>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:31:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>502</v>
+      </c>
+      <c r="E714" t="n">
+        <v>7</v>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:31:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>502</v>
+      </c>
+      <c r="E715" t="n">
+        <v>7</v>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:32:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>502</v>
+      </c>
+      <c r="E716" t="n">
+        <v>7</v>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:32:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>502</v>
+      </c>
+      <c r="E717" t="n">
+        <v>7</v>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:32:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>502</v>
+      </c>
+      <c r="E718" t="n">
+        <v>7</v>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:33:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>502</v>
+      </c>
+      <c r="E719" t="n">
+        <v>7</v>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:33:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>502</v>
+      </c>
+      <c r="E720" t="n">
+        <v>7</v>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:34:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>502</v>
+      </c>
+      <c r="E721" t="n">
+        <v>7</v>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:34:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>502</v>
+      </c>
+      <c r="E722" t="n">
+        <v>7</v>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:34:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>502</v>
+      </c>
+      <c r="E723" t="n">
+        <v>7</v>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:35:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=DF090054B4900CA447E3355783E7870B?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>502</v>
+      </c>
+      <c r="E724" t="n">
+        <v>7</v>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>502</v>
+      </c>
+      <c r="E725" t="n">
+        <v>7</v>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:35:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>502</v>
+      </c>
+      <c r="E726" t="n">
+        <v>7</v>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:36:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>502</v>
+      </c>
+      <c r="E727" t="n">
+        <v>7</v>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:36:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>502</v>
+      </c>
+      <c r="E728" t="n">
+        <v>7</v>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:37:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>502</v>
+      </c>
+      <c r="E729" t="n">
+        <v>7</v>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:37:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>0</v>
+      </c>
+      <c r="E730" t="n">
+        <v>7</v>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:40:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=EAEBD560DC4239882DA7DDF8DB7581CB?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=JANEIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>0</v>
+      </c>
+      <c r="E731" t="n">
+        <v>7</v>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>2026-08-03 08:42:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=705A7F37415969BD25F3DCF411CA5E1B?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=MARCO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>0</v>
+      </c>
+      <c r="E732" t="n">
+        <v>7</v>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>2026-08-03 14:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=9257E2A3BAAB0AD3CFC2D2BFDCA6F0DE?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>0</v>
+      </c>
+      <c r="E733" t="n">
+        <v>7</v>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>2026-08-03 18:38:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F733"/>
+  <dimension ref="A1:F774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20944,6 +20944,1154 @@
         </is>
       </c>
     </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>502</v>
+      </c>
+      <c r="E734" t="n">
+        <v>7</v>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:47:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>502</v>
+      </c>
+      <c r="E735" t="n">
+        <v>7</v>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:48:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>502</v>
+      </c>
+      <c r="E736" t="n">
+        <v>7</v>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>502</v>
+      </c>
+      <c r="E737" t="n">
+        <v>7</v>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:48:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>502</v>
+      </c>
+      <c r="E738" t="n">
+        <v>7</v>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:49:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>502</v>
+      </c>
+      <c r="E739" t="n">
+        <v>7</v>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:49:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>502</v>
+      </c>
+      <c r="E740" t="n">
+        <v>7</v>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:49:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>502</v>
+      </c>
+      <c r="E741" t="n">
+        <v>7</v>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:50:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>502</v>
+      </c>
+      <c r="E742" t="n">
+        <v>7</v>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:51:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7BDAA73F83352A0AF37B7DBFA299E9F?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>502</v>
+      </c>
+      <c r="E743" t="n">
+        <v>7</v>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:51:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>502</v>
+      </c>
+      <c r="E744" t="n">
+        <v>7</v>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:51:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>502</v>
+      </c>
+      <c r="E745" t="n">
+        <v>7</v>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:52:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=2&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>502</v>
+      </c>
+      <c r="E746" t="n">
+        <v>7</v>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:52:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>502</v>
+      </c>
+      <c r="E747" t="n">
+        <v>7</v>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:52:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>502</v>
+      </c>
+      <c r="E748" t="n">
+        <v>7</v>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:53:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>502</v>
+      </c>
+      <c r="E749" t="n">
+        <v>7</v>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:53:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>502</v>
+      </c>
+      <c r="E750" t="n">
+        <v>7</v>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:54:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>502</v>
+      </c>
+      <c r="E751" t="n">
+        <v>7</v>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>502</v>
+      </c>
+      <c r="E752" t="n">
+        <v>7</v>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:54:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>502</v>
+      </c>
+      <c r="E753" t="n">
+        <v>7</v>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:55:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>502</v>
+      </c>
+      <c r="E754" t="n">
+        <v>7</v>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:55:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>502</v>
+      </c>
+      <c r="E755" t="n">
+        <v>7</v>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:56:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>502</v>
+      </c>
+      <c r="E756" t="n">
+        <v>7</v>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>502</v>
+      </c>
+      <c r="E757" t="n">
+        <v>7</v>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:57:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>502</v>
+      </c>
+      <c r="E758" t="n">
+        <v>7</v>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:57:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E797095F6C4C2B6E6E52781044B58566?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=13&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>502</v>
+      </c>
+      <c r="E759" t="n">
+        <v>7</v>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:57:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=1&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>502</v>
+      </c>
+      <c r="E760" t="n">
+        <v>7</v>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:58:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=3&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>502</v>
+      </c>
+      <c r="E761" t="n">
+        <v>7</v>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=4&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>502</v>
+      </c>
+      <c r="E762" t="n">
+        <v>7</v>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:58:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=5&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>502</v>
+      </c>
+      <c r="E763" t="n">
+        <v>7</v>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:59:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=6&amp;formulario.exercicio=2025&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>502</v>
+      </c>
+      <c r="E764" t="n">
+        <v>7</v>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:59:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=1&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>502</v>
+      </c>
+      <c r="E765" t="n">
+        <v>7</v>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>2026-08-04 06:59:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=2&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>502</v>
+      </c>
+      <c r="E766" t="n">
+        <v>7</v>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:00:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=5&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>502</v>
+      </c>
+      <c r="E767" t="n">
+        <v>7</v>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:00:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=6&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>502</v>
+      </c>
+      <c r="E768" t="n">
+        <v>7</v>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:01:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=7&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>502</v>
+      </c>
+      <c r="E769" t="n">
+        <v>7</v>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:01:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=8&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>502</v>
+      </c>
+      <c r="E770" t="n">
+        <v>7</v>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:02:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>502</v>
+      </c>
+      <c r="E771" t="n">
+        <v>7</v>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:02:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=10&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>502</v>
+      </c>
+      <c r="E772" t="n">
+        <v>7</v>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:03:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=11&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>0</v>
+      </c>
+      <c r="E773" t="n">
+        <v>7</v>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:05:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=CA1BCD19B361EB72DD954D322A3344BD?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=12&amp;formulario.mes=OUTUBRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>0</v>
+      </c>
+      <c r="E774" t="n">
+        <v>7</v>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>2026-08-04 07:07:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F396"/>
+  <dimension ref="A1:F449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11508,6 +11508,1490 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>502</v>
+      </c>
+      <c r="E397" t="n">
+        <v>7</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:28:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>502</v>
+      </c>
+      <c r="E398" t="n">
+        <v>7</v>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:29:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>502</v>
+      </c>
+      <c r="E399" t="n">
+        <v>7</v>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:29:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>502</v>
+      </c>
+      <c r="E400" t="n">
+        <v>7</v>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:30:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>502</v>
+      </c>
+      <c r="E401" t="n">
+        <v>7</v>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:30:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>502</v>
+      </c>
+      <c r="E402" t="n">
+        <v>7</v>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:30:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>502</v>
+      </c>
+      <c r="E403" t="n">
+        <v>7</v>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:31:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>502</v>
+      </c>
+      <c r="E404" t="n">
+        <v>7</v>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:31:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>502</v>
+      </c>
+      <c r="E405" t="n">
+        <v>7</v>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>502</v>
+      </c>
+      <c r="E406" t="n">
+        <v>7</v>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>502</v>
+      </c>
+      <c r="E407" t="n">
+        <v>7</v>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>502</v>
+      </c>
+      <c r="E408" t="n">
+        <v>7</v>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>502</v>
+      </c>
+      <c r="E409" t="n">
+        <v>7</v>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>502</v>
+      </c>
+      <c r="E410" t="n">
+        <v>7</v>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=4A5ED5CF8E13D5514DDA565BB11A52C6?d-5470-p=4&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>502</v>
+      </c>
+      <c r="E411" t="n">
+        <v>7</v>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:33:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>502</v>
+      </c>
+      <c r="E412" t="n">
+        <v>7</v>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:33:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>502</v>
+      </c>
+      <c r="E413" t="n">
+        <v>7</v>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:33:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>502</v>
+      </c>
+      <c r="E414" t="n">
+        <v>7</v>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:34:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>502</v>
+      </c>
+      <c r="E415" t="n">
+        <v>7</v>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:34:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>502</v>
+      </c>
+      <c r="E416" t="n">
+        <v>7</v>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:34:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>502</v>
+      </c>
+      <c r="E417" t="n">
+        <v>7</v>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:34:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>502</v>
+      </c>
+      <c r="E418" t="n">
+        <v>7</v>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:35:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=6&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>502</v>
+      </c>
+      <c r="E419" t="n">
+        <v>7</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:35:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>502</v>
+      </c>
+      <c r="E420" t="n">
+        <v>7</v>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:35:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=1&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>502</v>
+      </c>
+      <c r="E421" t="n">
+        <v>7</v>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:35:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=2&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>502</v>
+      </c>
+      <c r="E422" t="n">
+        <v>7</v>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:35:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>502</v>
+      </c>
+      <c r="E423" t="n">
+        <v>7</v>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:36:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=5&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>502</v>
+      </c>
+      <c r="E424" t="n">
+        <v>7</v>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:36:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>502</v>
+      </c>
+      <c r="E425" t="n">
+        <v>7</v>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:36:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=6&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>502</v>
+      </c>
+      <c r="E426" t="n">
+        <v>7</v>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:36:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>502</v>
+      </c>
+      <c r="E427" t="n">
+        <v>7</v>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:36:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=7&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>502</v>
+      </c>
+      <c r="E428" t="n">
+        <v>7</v>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:37:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>502</v>
+      </c>
+      <c r="E429" t="n">
+        <v>7</v>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:37:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=8&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>502</v>
+      </c>
+      <c r="E430" t="n">
+        <v>7</v>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>502</v>
+      </c>
+      <c r="E431" t="n">
+        <v>7</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:37:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>502</v>
+      </c>
+      <c r="E432" t="n">
+        <v>7</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:38:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>502</v>
+      </c>
+      <c r="E433" t="n">
+        <v>7</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:38:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=10&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>502</v>
+      </c>
+      <c r="E434" t="n">
+        <v>7</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:38:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>502</v>
+      </c>
+      <c r="E435" t="n">
+        <v>7</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:38:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=11&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>502</v>
+      </c>
+      <c r="E436" t="n">
+        <v>7</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>502</v>
+      </c>
+      <c r="E437" t="n">
+        <v>7</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:39:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=12&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>502</v>
+      </c>
+      <c r="E438" t="n">
+        <v>7</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:39:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>502</v>
+      </c>
+      <c r="E439" t="n">
+        <v>7</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:39:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=C39AD1E3BFBCB63FE531992FE0E7A516?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2024&amp;d-5470-e=13&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>502</v>
+      </c>
+      <c r="E440" t="n">
+        <v>7</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:40:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=1&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>502</v>
+      </c>
+      <c r="E441" t="n">
+        <v>7</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:40:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>502</v>
+      </c>
+      <c r="E442" t="n">
+        <v>7</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:41:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=5&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>502</v>
+      </c>
+      <c r="E443" t="n">
+        <v>7</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:41:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>502</v>
+      </c>
+      <c r="E444" t="n">
+        <v>7</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:42:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=2&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>504</v>
+      </c>
+      <c r="E445" t="n">
+        <v>7</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:42:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>0</v>
+      </c>
+      <c r="E446" t="n">
+        <v>7</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:44:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=3&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>504</v>
+      </c>
+      <c r="E447" t="n">
+        <v>7</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:45:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>0</v>
+      </c>
+      <c r="E448" t="n">
+        <v>7</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=AEE004CD5D564E5ABE7C947A2B0DBE85?d-5470-p=4&amp;formulario.exercicio=2024&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>504</v>
+      </c>
+      <c r="E449" t="n">
+        <v>7</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2026-08-05 06:47:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/abatia/erros_varredura.xlsx
+++ b/resultados/abatia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F749"/>
+  <dimension ref="A1:F811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21392,6 +21392,1742 @@
         </is>
       </c>
     </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>502</v>
+      </c>
+      <c r="E750" t="n">
+        <v>5</v>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:04:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>502</v>
+      </c>
+      <c r="E751" t="n">
+        <v>5</v>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=11&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>502</v>
+      </c>
+      <c r="E752" t="n">
+        <v>5</v>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=12&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>502</v>
+      </c>
+      <c r="E753" t="n">
+        <v>5</v>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:04:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=12&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>502</v>
+      </c>
+      <c r="E754" t="n">
+        <v>5</v>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:05:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>502</v>
+      </c>
+      <c r="E755" t="n">
+        <v>5</v>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:05:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=434E6D99FC6A72DA365F826530F7E2FA?d-5470-p=5&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>502</v>
+      </c>
+      <c r="E756" t="n">
+        <v>5</v>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:05:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=1&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>502</v>
+      </c>
+      <c r="E757" t="n">
+        <v>5</v>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:05:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=2&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>502</v>
+      </c>
+      <c r="E758" t="n">
+        <v>5</v>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:06:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=2&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>502</v>
+      </c>
+      <c r="E759" t="n">
+        <v>5</v>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:06:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>502</v>
+      </c>
+      <c r="E760" t="n">
+        <v>5</v>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:06:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>502</v>
+      </c>
+      <c r="E761" t="n">
+        <v>5</v>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:06:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=6&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>502</v>
+      </c>
+      <c r="E762" t="n">
+        <v>5</v>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:07:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=7&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>502</v>
+      </c>
+      <c r="E763" t="n">
+        <v>5</v>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:07:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=7&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>502</v>
+      </c>
+      <c r="E764" t="n">
+        <v>5</v>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:07:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>502</v>
+      </c>
+      <c r="E765" t="n">
+        <v>5</v>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:08:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>502</v>
+      </c>
+      <c r="E766" t="n">
+        <v>5</v>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:08:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>502</v>
+      </c>
+      <c r="E767" t="n">
+        <v>5</v>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:08:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>502</v>
+      </c>
+      <c r="E768" t="n">
+        <v>5</v>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:08:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>502</v>
+      </c>
+      <c r="E769" t="n">
+        <v>5</v>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:09:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=11&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>502</v>
+      </c>
+      <c r="E770" t="n">
+        <v>5</v>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:09:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=11&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>502</v>
+      </c>
+      <c r="E771" t="n">
+        <v>5</v>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=12&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>502</v>
+      </c>
+      <c r="E772" t="n">
+        <v>5</v>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:09:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>502</v>
+      </c>
+      <c r="E773" t="n">
+        <v>5</v>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:10:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E7CF31C3FFA1E905F631938706CC59F1?d-5470-p=6&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=MAIO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>502</v>
+      </c>
+      <c r="E774" t="n">
+        <v>5</v>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:10:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=1&amp;formulario.exercicio=2015&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>502</v>
+      </c>
+      <c r="E775" t="n">
+        <v>5</v>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:10:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=1&amp;formulario.exercicio=2015&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>502</v>
+      </c>
+      <c r="E776" t="n">
+        <v>5</v>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:10:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=1&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>502</v>
+      </c>
+      <c r="E777" t="n">
+        <v>5</v>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=2&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>502</v>
+      </c>
+      <c r="E778" t="n">
+        <v>5</v>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:11:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=2&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>502</v>
+      </c>
+      <c r="E779" t="n">
+        <v>5</v>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:11:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>502</v>
+      </c>
+      <c r="E780" t="n">
+        <v>5</v>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:12:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>502</v>
+      </c>
+      <c r="E781" t="n">
+        <v>5</v>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=6&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>502</v>
+      </c>
+      <c r="E782" t="n">
+        <v>5</v>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=7&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>502</v>
+      </c>
+      <c r="E783" t="n">
+        <v>5</v>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:12:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=7&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>502</v>
+      </c>
+      <c r="E784" t="n">
+        <v>5</v>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:13:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>502</v>
+      </c>
+      <c r="E785" t="n">
+        <v>5</v>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>502</v>
+      </c>
+      <c r="E786" t="n">
+        <v>5</v>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>502</v>
+      </c>
+      <c r="E787" t="n">
+        <v>5</v>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:13:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>502</v>
+      </c>
+      <c r="E788" t="n">
+        <v>5</v>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:14:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D789" t="n">
+        <v>502</v>
+      </c>
+      <c r="E789" t="n">
+        <v>5</v>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:14:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=11&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D790" t="n">
+        <v>502</v>
+      </c>
+      <c r="E790" t="n">
+        <v>5</v>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:14:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=11&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>502</v>
+      </c>
+      <c r="E791" t="n">
+        <v>5</v>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:14:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=12&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>502</v>
+      </c>
+      <c r="E792" t="n">
+        <v>5</v>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:14:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>502</v>
+      </c>
+      <c r="E793" t="n">
+        <v>5</v>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:15:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=BD11C85E7E72EC1A1F24E2BCF8AB614D?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=13&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>502</v>
+      </c>
+      <c r="E794" t="n">
+        <v>5</v>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:15:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=1&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>502</v>
+      </c>
+      <c r="E795" t="n">
+        <v>5</v>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=1&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>502</v>
+      </c>
+      <c r="E796" t="n">
+        <v>5</v>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:16:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=2&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>502</v>
+      </c>
+      <c r="E797" t="n">
+        <v>5</v>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:16:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>502</v>
+      </c>
+      <c r="E798" t="n">
+        <v>5</v>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=5&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>502</v>
+      </c>
+      <c r="E799" t="n">
+        <v>5</v>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=6&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>502</v>
+      </c>
+      <c r="E800" t="n">
+        <v>5</v>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=6&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
+        <v>502</v>
+      </c>
+      <c r="E801" t="n">
+        <v>5</v>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:17:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=7&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D802" t="n">
+        <v>502</v>
+      </c>
+      <c r="E802" t="n">
+        <v>5</v>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:17:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>HTTP_502</t>
+        </is>
+      </c>
+      <c r="D803" t="n">
+        <v>502</v>
+      </c>
+      <c r="E803" t="n">
+        <v>5</v>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:18:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=8&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D804" t="n">
+        <v>504</v>
+      </c>
+      <c r="E804" t="n">
+        <v>5</v>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:19:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D805" t="n">
+        <v>0</v>
+      </c>
+      <c r="E805" t="n">
+        <v>5</v>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=9&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D806" t="n">
+        <v>504</v>
+      </c>
+      <c r="E806" t="n">
+        <v>5</v>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:21:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D807" t="n">
+        <v>0</v>
+      </c>
+      <c r="E807" t="n">
+        <v>5</v>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:23:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=0A5938966E642C0E0909A84047CD558A?d-5470-p=3&amp;6578706f7274=1&amp;formulario.exercicio=2015&amp;d-5470-e=10&amp;formulario.mes=JUNHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>HTTP_504</t>
+        </is>
+      </c>
+      <c r="D808" t="n">
+        <v>504</v>
+      </c>
+      <c r="E808" t="n">
+        <v>5</v>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>2026-08-07 07:24:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=E87AD89AA983E97A596012B19CFA0006?d-5470-p=2&amp;6578706f7274=1&amp;formulario.exercicio=2010&amp;d-5470-e=9&amp;formulario.mes=FEVEREIRO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D809" t="n">
+        <v>0</v>
+      </c>
+      <c r="E809" t="n">
+        <v>5</v>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>2026-08-07 11:38:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=3F5D566F8195F97960FD8EFE8C2B696D?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2025&amp;d-5470-e=9&amp;formulario.mes=AGOSTO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: SessionNotCreatedException</t>
+        </is>
+      </c>
+      <c r="D810" t="n">
+        <v>0</v>
+      </c>
+      <c r="E810" t="n">
+        <v>6</v>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:29:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>abatia</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>https://abatia.metajuris.com.br/transparencia/srhRelacaoDeServidoresAtivos/listData;jsessionid=46409B376C4CE6FF8D2EBFA2076F0E29?d-5470-p=1&amp;6578706f7274=1&amp;formulario.exercicio=2013&amp;d-5470-e=9&amp;formulario.mes=JULHO&amp;formulario.codEntidade=249</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: ReadTimeoutError</t>
+        </is>
+      </c>
+      <c r="D811" t="n">
+        <v>0</v>
+      </c>
+      <c r="E811" t="n">
+        <v>6</v>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:39:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
